--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_OV.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_OV.xlsx
@@ -564,7 +564,7 @@
         <v>0.430288162070488</v>
       </c>
       <c r="E12">
-        <v>0.6630645759324548</v>
+        <v>0.663064575932455</v>
       </c>
     </row>
     <row r="13" spans="1:5">

--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_OV.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_OV.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.936061968566015</v>
+        <v>3.162992627914984</v>
       </c>
       <c r="C2">
-        <v>1.313498814969672</v>
+        <v>2.088643554173683</v>
       </c>
       <c r="D2">
-        <v>1.487638583328825</v>
+        <v>1.218616516163972</v>
       </c>
       <c r="E2">
-        <v>1.594702201724019</v>
+        <v>0.858045275677326</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0.8665389055668421</v>
+        <v>1.64254341377968</v>
       </c>
       <c r="C3">
-        <v>1.225690816709213</v>
+        <v>1.258487801393642</v>
       </c>
       <c r="D3">
-        <v>1.408310378582805</v>
+        <v>1.189660932851027</v>
       </c>
       <c r="E3">
-        <v>1.531761101935835</v>
+        <v>1.166135030353595</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0.5220626417996851</v>
+        <v>1.2734664862426</v>
       </c>
       <c r="C4">
-        <v>0.7754902945783939</v>
+        <v>1.005688466232191</v>
       </c>
       <c r="D4">
-        <v>1.005622767603824</v>
+        <v>0.8176712842551797</v>
       </c>
       <c r="E4">
-        <v>1.170512505105007</v>
+        <v>0.7372996663735116</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.3813872425663433</v>
+        <v>0.09505161927737039</v>
       </c>
       <c r="C5">
-        <v>0.449441296965801</v>
+        <v>0.1127081890223835</v>
       </c>
       <c r="D5">
-        <v>0.4406486889174661</v>
+        <v>0.1098211128726193</v>
       </c>
       <c r="E5">
-        <v>0.4105244968136729</v>
+        <v>0.1029488676220047</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0.3079900402865606</v>
+        <v>0.3390609853169292</v>
       </c>
       <c r="C6">
-        <v>0.3270940533934479</v>
+        <v>0.2833512926140652</v>
       </c>
       <c r="D6">
-        <v>0.2990603850972823</v>
+        <v>0.2821975544014355</v>
       </c>
       <c r="E6">
-        <v>0.2511295960563111</v>
+        <v>0.2864671041285006</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.343939944676575</v>
+        <v>0.6534858948854926</v>
       </c>
       <c r="C7">
-        <v>0.4013754906414626</v>
+        <v>0.3813067161093896</v>
       </c>
       <c r="D7">
-        <v>0.4173120270607643</v>
+        <v>0.3604058415524781</v>
       </c>
       <c r="E7">
-        <v>0.3828568701346464</v>
+        <v>0.3030950221899285</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.2001018367653793</v>
+        <v>0.05001026773698974</v>
       </c>
       <c r="C8">
-        <v>0.2902973021720563</v>
+        <v>0.0726404424505844</v>
       </c>
       <c r="D8">
-        <v>0.3108452978446444</v>
+        <v>0.07768772551659349</v>
       </c>
       <c r="E8">
-        <v>0.3144157603848184</v>
+        <v>0.07858007008706515</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.5951509372527959</v>
+        <v>1.105182944241474</v>
       </c>
       <c r="C9">
-        <v>0.688065013977329</v>
+        <v>0.8010999115917771</v>
       </c>
       <c r="D9">
-        <v>0.5882943898208607</v>
+        <v>0.5039983501522117</v>
       </c>
       <c r="E9">
-        <v>0.4907369594154016</v>
+        <v>0.3422358291146481</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.4861278178718842</v>
+        <v>0.1222344513146067</v>
       </c>
       <c r="C10">
-        <v>0.793999102161678</v>
+        <v>0.1973523779939431</v>
       </c>
       <c r="D10">
-        <v>1.107204519682487</v>
+        <v>0.2784011364519547</v>
       </c>
       <c r="E10">
-        <v>1.371529122152553</v>
+        <v>0.3409003020379177</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.42736632153673</v>
+        <v>0.1102880829772206</v>
       </c>
       <c r="C11">
-        <v>0.6895836588783807</v>
+        <v>0.1668347561802534</v>
       </c>
       <c r="D11">
-        <v>0.988328355728557</v>
+        <v>0.2391116989665864</v>
       </c>
       <c r="E11">
-        <v>1.251478324715245</v>
+        <v>0.3229621483136118</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.1055451499878177</v>
+        <v>0.09817196735541382</v>
       </c>
       <c r="C12">
-        <v>0.1984769673372521</v>
+        <v>0.1698435149308966</v>
       </c>
       <c r="D12">
-        <v>0.430288162070488</v>
+        <v>0.4350118363040388</v>
       </c>
       <c r="E12">
-        <v>0.663064575932455</v>
+        <v>0.8688836713098501</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.3713265864090526</v>
+        <v>0.09330770632842858</v>
       </c>
       <c r="C13">
-        <v>0.6163823604628738</v>
+        <v>0.1517248887293227</v>
       </c>
       <c r="D13">
-        <v>0.9258688481323134</v>
+        <v>0.2326542233768378</v>
       </c>
       <c r="E13">
-        <v>1.200349245239656</v>
+        <v>0.3016262205986827</v>
       </c>
     </row>
   </sheetData>
